--- a/datos/Bot Descargas.xlsx
+++ b/datos/Bot Descargas.xlsx
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matriculas</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -2887,17 +2887,17 @@
       <c r="G6" s="6" t="n"/>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matriculas</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Sede - jornada</t>
+          <t>Período</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>B2G - Única</t>
+          <t>B2G_YES BOGOTA-2 C1_SEP_2026</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matriculas</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Programa</t>
+          <t>Sede - jornada</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>YES BOGOTA 2026-2</t>
+          <t>B2G - Única</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matriculas</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Período</t>
+          <t>Programa</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>B2G_YES BOGOTA-2 C1_SEP_2026</t>
+          <t>YES BOGOTA 2026-2</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -3001,17 +3001,17 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matriculas</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Curso</t>
+          <t>¿Incluir cursos archivados?</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matriculas</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Inasistencias por curso</t>
+          <t>Detalle actualizado matriculas</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
